--- a/docs/Mapping_casi_uso/matrimoni/Matr_998_4.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_998_4.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="55">
   <si>
     <t>Sezione</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>descrizioneMotivoRecupero</t>
+  </si>
+  <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
   </si>
   <si>
     <t>Evento da annotare</t>
@@ -229,7 +235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -519,19 +525,19 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -542,16 +548,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>40</v>
@@ -565,7 +571,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>41</v>
@@ -574,7 +580,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -588,7 +594,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
@@ -597,7 +603,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -611,7 +617,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
@@ -620,10 +626,10 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>10</v>
@@ -634,19 +640,19 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>10</v>
@@ -657,7 +663,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>48</v>
@@ -666,10 +672,10 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
@@ -680,19 +686,19 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -703,13 +709,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -721,6 +727,29 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/matrimoni/Matr_998_4.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_998_4.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="65">
   <si>
     <t>Sezione</t>
   </si>
@@ -161,6 +161,12 @@
     <t>nomeComuneRegistrazione</t>
   </si>
   <si>
+    <t>Tipo evento</t>
+  </si>
+  <si>
+    <t>idtipocontenuto</t>
+  </si>
+  <si>
     <t>Numero Comunale</t>
   </si>
   <si>
@@ -171,6 +177,24 @@
   </si>
   <si>
     <t>Data atto</t>
+  </si>
+  <si>
+    <t>Parte</t>
+  </si>
+  <si>
+    <t>parte</t>
+  </si>
+  <si>
+    <t>Serie</t>
+  </si>
+  <si>
+    <t>serie</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>volume</t>
   </si>
   <si>
     <t>Composizione libera</t>
@@ -241,7 +265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -675,13 +699,13 @@
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
@@ -695,7 +719,7 @@
         <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
@@ -704,7 +728,7 @@
         <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -727,7 +751,7 @@
         <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>10</v>
@@ -738,19 +762,19 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
@@ -761,7 +785,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>55</v>
@@ -770,7 +794,7 @@
         <v>25</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>56</v>
@@ -779,6 +803,98 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>16</v>
       </c>
     </row>
